--- a/Models/Овцы и козы/results/Овцы и козы - Результаты прогнозов ХВ средние.xlsx
+++ b/Models/Овцы и козы/results/Овцы и козы - Результаты прогнозов ХВ средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57.42</v>
+        <v>82.03</v>
       </c>
       <c r="C2" t="n">
-        <v>49.23</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>112.58</v>
+        <v>139.36</v>
       </c>
       <c r="C3" t="n">
-        <v>94.29000000000001</v>
+        <v>97.03</v>
       </c>
       <c r="D3" t="n">
-        <v>5.63</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>411.2</v>
+        <v>350.71</v>
       </c>
       <c r="C4" t="n">
-        <v>338.01</v>
+        <v>288.23</v>
       </c>
       <c r="D4" t="n">
-        <v>14.43</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.36</v>
+        <v>103.65</v>
       </c>
       <c r="C5" t="n">
-        <v>55.91</v>
+        <v>76.98</v>
       </c>
       <c r="D5" t="n">
-        <v>6.38</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>136.14</v>
+        <v>148.5</v>
       </c>
       <c r="C6" t="n">
-        <v>115.87</v>
+        <v>110.22</v>
       </c>
       <c r="D6" t="n">
-        <v>9.09</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="7">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.41</v>
+        <v>1.15</v>
       </c>
       <c r="C7" t="n">
-        <v>0.37</v>
+        <v>0.95</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="C8" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="D8" t="n">
-        <v>16.22</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="9">
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.15</v>
+        <v>12.76</v>
       </c>
       <c r="C9" t="n">
-        <v>25.06</v>
+        <v>10.31</v>
       </c>
       <c r="D9" t="n">
-        <v>24.58</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="10">
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>177.04</v>
+        <v>119.88</v>
       </c>
       <c r="C10" t="n">
-        <v>166.39</v>
+        <v>104.4</v>
       </c>
       <c r="D10" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -599,13 +599,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26.8</v>
+        <v>22.72</v>
       </c>
       <c r="C11" t="n">
-        <v>23.68</v>
+        <v>18.57</v>
       </c>
       <c r="D11" t="n">
-        <v>2.01</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="12">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>65.55</v>
+        <v>74.22</v>
       </c>
       <c r="C12" t="n">
-        <v>58.28</v>
+        <v>60.61</v>
       </c>
       <c r="D12" t="n">
-        <v>7.37</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="13">
@@ -631,13 +631,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51.54</v>
+        <v>51.81</v>
       </c>
       <c r="C13" t="n">
-        <v>43.29</v>
+        <v>43.81</v>
       </c>
       <c r="D13" t="n">
-        <v>20.26</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="14">
@@ -647,13 +647,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>92.76000000000001</v>
+        <v>87</v>
       </c>
       <c r="C14" t="n">
-        <v>80.69</v>
+        <v>78.45</v>
       </c>
       <c r="D14" t="n">
-        <v>16.8</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="15">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.48</v>
+        <v>22.68</v>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>20.89</v>
       </c>
       <c r="D15" t="n">
-        <v>9.15</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="16">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>94.44</v>
+        <v>197.65</v>
       </c>
       <c r="C16" t="n">
-        <v>70.7</v>
+        <v>161.85</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>75.95</v>
+        <v>152.99</v>
       </c>
       <c r="C17" t="n">
-        <v>61.31</v>
+        <v>115.6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.97</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="18">
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>73.42</v>
+        <v>67.41</v>
       </c>
       <c r="C18" t="n">
-        <v>62.11</v>
+        <v>54.34</v>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="19">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34.42</v>
+        <v>30.58</v>
       </c>
       <c r="C19" t="n">
-        <v>28.86</v>
+        <v>23.56</v>
       </c>
       <c r="D19" t="n">
-        <v>3.48</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="20">
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33.23</v>
+        <v>25.49</v>
       </c>
       <c r="C20" t="n">
-        <v>29.05</v>
+        <v>23.51</v>
       </c>
       <c r="D20" t="n">
-        <v>8.42</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>752.37</v>
+        <v>623.35</v>
       </c>
       <c r="C21" t="n">
-        <v>679.64</v>
+        <v>478.33</v>
       </c>
       <c r="D21" t="n">
-        <v>17.16</v>
+        <v>8.41</v>
       </c>
     </row>
   </sheetData>
